--- a/ONCHO/Entomological survey Survey/Nigeria/2024/bauchi/nov 2024/ng_oncho_2411_4_b_lab_bau.xlsx
+++ b/ONCHO/Entomological survey Survey/Nigeria/2024/bauchi/nov 2024/ng_oncho_2411_4_b_lab_bau.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yumbad\Repositories\dsa-forms\ONCHO\Entomological survey Survey\Nigeria\2024\bauchi\nov 2024\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1C61B16-4DE1-43E9-89BD-34E8B1F144F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CB37D72-0B45-4055-9CCB-41B329BA1F1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="survey" sheetId="1" r:id="rId1"/>
